--- a/src/Accounting.Web/Templates/GeneralAccountDataTemplateHant.xlsx
+++ b/src/Accounting.Web/Templates/GeneralAccountDataTemplateHant.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22871" windowHeight="8580"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="83">
   <si>
     <t>Code</t>
   </si>
@@ -40,7 +40,7 @@
     <t>OtherName</t>
   </si>
   <si>
-    <t>ParentCode</t>
+    <t>Parent</t>
   </si>
   <si>
     <t>ShowDetail</t>
@@ -52,7 +52,7 @@
     <t>Level</t>
   </si>
   <si>
-    <t>AccountTypeCode</t>
+    <t>AccountType</t>
   </si>
   <si>
     <t>Description</t>
@@ -64,6 +64,9 @@
     <t>Non-current Assets</t>
   </si>
   <si>
+    <t>DR</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
@@ -137,6 +140,9 @@
   </si>
   <si>
     <t>Non-current Liabilities</t>
+  </si>
+  <si>
+    <t>CR</t>
   </si>
   <si>
     <t>NL</t>
@@ -1206,6 +1212,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="42.2222222222222" customWidth="1"/>
+    <col min="4" max="5" width="11.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="17.5555555555556" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1250,14 +1260,14 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1265,10 +1275,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1276,14 +1286,14 @@
       <c r="E3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>1</v>
+      <c r="F3" t="s">
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1291,10 +1301,10 @@
         <v>111</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>11</v>
@@ -1302,14 +1312,14 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="F4" t="s">
+        <v>11</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1317,10 +1327,10 @@
         <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>11</v>
@@ -1328,14 +1338,14 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>1</v>
+      <c r="F5" t="s">
+        <v>11</v>
       </c>
       <c r="G5">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1343,10 +1353,10 @@
         <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>11</v>
@@ -1354,14 +1364,14 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>1</v>
+      <c r="F6" t="s">
+        <v>11</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1369,10 +1379,10 @@
         <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>11</v>
@@ -1380,14 +1390,14 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7">
-        <v>1</v>
+      <c r="F7" t="s">
+        <v>11</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1395,10 +1405,10 @@
         <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>11</v>
@@ -1406,14 +1416,14 @@
       <c r="E8">
         <v>1</v>
       </c>
-      <c r="F8">
-        <v>1</v>
+      <c r="F8" t="s">
+        <v>11</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1421,10 +1431,10 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1432,14 +1442,14 @@
       <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9">
-        <v>1</v>
+      <c r="F9" t="s">
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1447,10 +1457,10 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1458,14 +1468,14 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10">
-        <v>1</v>
+      <c r="F10" t="s">
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1473,22 +1483,22 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11">
-        <v>1</v>
+      <c r="F11" t="s">
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1496,10 +1506,10 @@
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1507,14 +1517,14 @@
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12">
-        <v>1</v>
+      <c r="F12" t="s">
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1522,22 +1532,22 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13">
-        <v>-1</v>
+      <c r="F13" t="s">
+        <v>37</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1545,10 +1555,10 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1556,14 +1566,14 @@
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="F14">
-        <v>-1</v>
+      <c r="F14" t="s">
+        <v>37</v>
       </c>
       <c r="G14">
         <v>2</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1571,10 +1581,10 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -1582,14 +1592,14 @@
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15">
-        <v>-1</v>
+      <c r="F15" t="s">
+        <v>37</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1597,10 +1607,10 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -1608,14 +1618,14 @@
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16">
-        <v>-1</v>
+      <c r="F16" t="s">
+        <v>37</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1623,10 +1633,10 @@
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -1634,14 +1644,14 @@
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17">
-        <v>-1</v>
+      <c r="F17" t="s">
+        <v>37</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1649,22 +1659,22 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18">
-        <v>-1</v>
+      <c r="F18" t="s">
+        <v>37</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1672,10 +1682,10 @@
         <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -1683,14 +1693,14 @@
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19">
-        <v>-1</v>
+      <c r="F19" t="s">
+        <v>37</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1698,10 +1708,10 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1709,14 +1719,14 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20">
-        <v>-1</v>
+      <c r="F20" t="s">
+        <v>37</v>
       </c>
       <c r="G20">
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1724,10 +1734,10 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -1735,14 +1745,14 @@
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21">
-        <v>-1</v>
+      <c r="F21" t="s">
+        <v>37</v>
       </c>
       <c r="G21">
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1750,22 +1760,22 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22">
-        <v>-1</v>
+      <c r="F22" t="s">
+        <v>37</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1773,22 +1783,22 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23">
-        <v>-1</v>
+      <c r="F23" t="s">
+        <v>37</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1796,22 +1806,22 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
-      <c r="F24">
-        <v>1</v>
+      <c r="F24" t="s">
+        <v>11</v>
       </c>
       <c r="G24">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1819,22 +1829,22 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
-      <c r="F25">
-        <v>1</v>
+      <c r="F25" t="s">
+        <v>11</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1842,10 +1852,10 @@
         <v>801</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -1853,14 +1863,14 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26">
-        <v>1</v>
+      <c r="F26" t="s">
+        <v>11</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1868,10 +1878,10 @@
         <v>802</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27">
         <v>8</v>
@@ -1879,14 +1889,14 @@
       <c r="E27">
         <v>1</v>
       </c>
-      <c r="F27">
-        <v>1</v>
+      <c r="F27" t="s">
+        <v>11</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1894,10 +1904,10 @@
         <v>803</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -1905,14 +1915,14 @@
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28">
-        <v>1</v>
+      <c r="F28" t="s">
+        <v>11</v>
       </c>
       <c r="G28">
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1920,10 +1930,10 @@
         <v>804</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D29">
         <v>8</v>
@@ -1931,14 +1941,14 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29">
-        <v>1</v>
+      <c r="F29" t="s">
+        <v>11</v>
       </c>
       <c r="G29">
         <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1946,10 +1956,10 @@
         <v>805</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D30">
         <v>8</v>
@@ -1957,14 +1967,14 @@
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30">
-        <v>1</v>
+      <c r="F30" t="s">
+        <v>11</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1972,10 +1982,10 @@
         <v>806</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -1983,14 +1993,14 @@
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31">
-        <v>1</v>
+      <c r="F31" t="s">
+        <v>11</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1998,10 +2008,10 @@
         <v>807</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D32">
         <v>8</v>
@@ -2009,14 +2019,14 @@
       <c r="E32">
         <v>1</v>
       </c>
-      <c r="F32">
-        <v>1</v>
+      <c r="F32" t="s">
+        <v>11</v>
       </c>
       <c r="G32">
         <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2024,25 +2034,33 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33">
-        <v>1</v>
+      <c r="F33" t="s">
+        <v>11</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
+      <formula1>"1,0"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F12 F13:F23 F24:F33 F34:F1048576">
+      <formula1>"DR,CR"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
